--- a/output/pdf_financials_xlsx/PHNM.xlsx
+++ b/output/pdf_financials_xlsx/PHNM.xlsx
@@ -6010,19 +6010,19 @@
         <v>4.608149</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>8.791623</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>10.519203</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>10.357732</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>11.295575</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>12.147069</v>
       </c>
     </row>
     <row r="93">
@@ -7491,19 +7491,19 @@
         <v>0</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>1.096912</v>
+        <v>-4.305549</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0.84841</v>
+        <v>-3.923271</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0.632172</v>
+        <v>-0.151778</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0</v>
+        <v>-1.547752</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0</v>
+        <v>-1.304924</v>
       </c>
     </row>
     <row r="119">
@@ -9611,7 +9611,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -10112,7 +10116,11 @@
           <t>Reserves 7, 9</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -10314,7 +10322,11 @@
           <t>Reserves 7,9</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -10979,7 +10991,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -17834,7 +17850,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PHNM.xlsx
+++ b/output/pdf_financials_xlsx/PHNM.xlsx
@@ -1029,31 +1029,31 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.007364</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.004999</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.010041</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.006551</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.005095</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.003774</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.003144</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.000167</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
@@ -1065,19 +1065,19 @@
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.002041</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.004829</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.002465</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.008694</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.013392</v>
       </c>
     </row>
     <row r="13">
@@ -1975,31 +1975,31 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.56006</v>
+        <v>-1.567424</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.800435</v>
+        <v>-0.805434</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.531074</v>
+        <v>-0.541115</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.392243</v>
+        <v>-2.398794</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.374665</v>
+        <v>-0.37976</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.840926</v>
+        <v>-0.8447</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-0.20057</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.321782</v>
+        <v>-0.324926</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.132692</v>
+        <v>-0.132859</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-0.594244</v>
@@ -2011,19 +2011,19 @@
         <v>-1.623196</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-2.765714</v>
+        <v>-2.767755</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-2.027621</v>
+        <v>-2.03245</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-1.866521</v>
+        <v>-1.868986</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-1.191106</v>
+        <v>-1.1998</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-1.007707</v>
+        <v>-1.021099</v>
       </c>
     </row>
     <row r="28">
@@ -2091,31 +2091,31 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.56006</v>
+        <v>-1.567424</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.800435</v>
+        <v>-0.805434</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.531074</v>
+        <v>-0.541115</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.392243</v>
+        <v>-2.398794</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.374665</v>
+        <v>-0.37976</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.840926</v>
+        <v>-0.8447</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-0.20057</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.321782</v>
+        <v>-0.324926</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.132692</v>
+        <v>-0.132859</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-0.594244</v>
@@ -2127,19 +2127,19 @@
         <v>-1.618806</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-2.746085</v>
+        <v>-2.748126</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-2.027621</v>
+        <v>-2.03245</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-1.866521</v>
+        <v>-1.868986</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-1.191106</v>
+        <v>-1.1998</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-1.007707</v>
+        <v>-1.021099</v>
       </c>
     </row>
     <row r="30">
@@ -2422,10 +2422,10 @@
         <v>0.280993</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.160156</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.784583</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>2.389327</v>
@@ -2434,19 +2434,19 @@
         <v>1.263901</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.437895</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.573655</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.403684</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.385089</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.5833970000000001</v>
       </c>
     </row>
     <row r="35">
@@ -2538,10 +2538,10 @@
         <v>0.282523</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.00136</v>
+        <v>0.161516</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.00153</v>
+        <v>0.786113</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>2.389327</v>
@@ -2550,19 +2550,19 @@
         <v>1.263901</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.437895</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.573655</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.403684</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.385089</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.5833970000000001</v>
       </c>
     </row>
     <row r="37">
@@ -3234,10 +3234,10 @@
         <v>0.001087</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.160156</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.819779</v>
+        <v>0.035196</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0.20336</v>
@@ -3246,19 +3246,19 @@
         <v>0.06850199999999999</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.543063</v>
+        <v>0.105168</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.628878</v>
+        <v>0.055223</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.409583</v>
+        <v>0.005899</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.40065</v>
+        <v>0.015561</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.617819</v>
+        <v>0.034422</v>
       </c>
     </row>
     <row r="49">
@@ -7841,7 +7841,7 @@
         <v>0</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.005784</v>
       </c>
       <c r="O124" s="3" t="n">
         <v>0</v>
@@ -7899,7 +7899,7 @@
         <v>0</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.005784</v>
       </c>
       <c r="O125" s="3" t="n">
         <v>0</v>
@@ -8687,7 +8687,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -23097,7 +23097,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
@@ -27148,7 +27152,11 @@
           <t>Proceeds from refund of reclamation deposits</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>
@@ -27249,7 +27257,11 @@
           <t>Realized foreign exchange on reclamation deposit</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -27918,7 +27930,11 @@
           <t>Proceeds from refund of reclamation deposit</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
@@ -28019,7 +28035,11 @@
           <t>Realized foreign exchange of reclamation deposit</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
@@ -37750,7 +37770,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -39951,7 +39971,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -42358,7 +42378,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E343" s="5" t="n">
@@ -43245,7 +43265,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">

--- a/output/pdf_financials_xlsx/PHNM.xlsx
+++ b/output/pdf_financials_xlsx/PHNM.xlsx
@@ -7110,7 +7110,7 @@
         <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.033625</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>0</v>
@@ -32847,7 +32847,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
           <t>-</t>
@@ -33455,7 +33459,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PHNM.xlsx
+++ b/output/pdf_financials_xlsx/PHNM.xlsx
@@ -739,55 +739,55 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.250827</v>
+        <v>0.288886</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.314302</v>
+        <v>0.357465</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.253376</v>
+        <v>0.275519</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.118335</v>
+        <v>0.129628</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.186227</v>
+        <v>0.202931</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.169521</v>
+        <v>0.186945</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.074799</v>
+        <v>0.099952</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.05712</v>
+        <v>0.073111</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.053351</v>
+        <v>0.061309</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.140447</v>
+        <v>0.145164</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.87086</v>
+        <v>0.974247</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.723496</v>
+        <v>0.861356</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.687097</v>
+        <v>0.740683</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.311114</v>
+        <v>0.369942</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.293513</v>
+        <v>0.357419</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.336246</v>
+        <v>0.420658</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.299503</v>
+        <v>0.444085</v>
       </c>
     </row>
     <row r="8">
@@ -913,43 +913,43 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.250827</v>
+        <v>0.288886</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.314302</v>
+        <v>0.357465</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.253376</v>
+        <v>0.275519</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.118335</v>
+        <v>0.129628</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.186227</v>
+        <v>0.202931</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.169521</v>
+        <v>0.186945</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.074799</v>
+        <v>0.099952</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.05712</v>
+        <v>0.073111</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.053351</v>
+        <v>0.061309</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.140447</v>
+        <v>0.145164</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.87086</v>
+        <v>0.974247</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.723496</v>
+        <v>0.861356</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.687097</v>
+        <v>0.740683</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>1.18404</v>
@@ -998,16 +998,16 @@
         <v>-0.132859</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.140447</v>
+        <v>-0.145164</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.87086</v>
+        <v>-0.974247</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.723496</v>
+        <v>-0.861356</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-0.687097</v>
+        <v>-0.740683</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>-1.18404</v>
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.13</v>
+        <v>-0.13</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>-0</v>
@@ -4230,19 +4230,19 @@
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.250055</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.001552</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.005561</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.02998</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.004665</v>
       </c>
       <c r="I64" s="3" t="n">
         <v>0</v>
@@ -4404,19 +4404,19 @@
         <v>0</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.038695</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.038681</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.062643</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.03753</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.05102</v>
       </c>
       <c r="I67" s="3" t="n">
         <v>0</v>
@@ -6505,7 +6505,7 @@
         <v>0.012965</v>
       </c>
       <c r="N101" s="3" t="n">
-        <v>0</v>
+        <v>0.011571</v>
       </c>
       <c r="O101" s="3" t="n">
         <v>-0.014901</v>
@@ -6795,7 +6795,7 @@
         <v>-1.15084</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>-0.038872</v>
+        <v>-0.027301</v>
       </c>
       <c r="O106" s="3" t="n">
         <v>0.103106</v>
@@ -7082,7 +7082,7 @@
         <v>0</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>0</v>
+        <v>-0.01317</v>
       </c>
       <c r="N111" s="3" t="n">
         <v>0</v>
@@ -7290,7 +7290,7 @@
         <v>0</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.0228</v>
       </c>
       <c r="F115" s="3" t="n">
         <v>0</v>
@@ -7299,7 +7299,7 @@
         <v>0</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I115" s="3" t="n">
         <v>0</v>
@@ -8458,7 +8458,7 @@
         <v>0</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>0</v>
+        <v>-0.01317</v>
       </c>
       <c r="N134" s="3" t="n">
         <v>0</v>
@@ -8524,7 +8524,7 @@
         <v>-1.332777</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>-1.270878</v>
+        <v>-1.284048</v>
       </c>
       <c r="N135" s="3" t="n">
         <v>-1.451002</v>
@@ -18143,7 +18143,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -18976,7 +18980,11 @@
           <t>Private placements 9,218,000 1,609,229 727,831</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -21386,7 +21394,11 @@
           <t>Proceeds from private placement (Note 7)</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -21893,7 +21905,11 @@
           <t>Shares issued for: cash pursuant to private placement 12,097,000 3,025,715 1,803,385</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -22998,7 +23014,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
@@ -23301,7 +23321,11 @@
           <t>Shares issued for: cash pursuant to private placement 15,000,000 4,157,361 1,842,639</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
@@ -25386,7 +25410,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
@@ -27831,7 +27859,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>
@@ -34067,7 +34099,11 @@
           <t>Pursuant to private placement 10,010,654 413,441 287,305</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E258" t="inlineStr">
         <is>
           <t>-</t>
@@ -35796,7 +35832,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E275" s="5" t="n">
         <v>-0.13</v>
       </c>
@@ -37091,7 +37131,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr"/>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E288" t="inlineStr">
         <is>
           <t>-</t>
@@ -39631,7 +39675,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr"/>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E314" t="inlineStr">
         <is>
           <t>-</t>
@@ -40369,7 +40417,11 @@
           <t>Directors fees 9</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr"/>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E322" t="inlineStr">
         <is>
           <t>-</t>
@@ -44081,7 +44133,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D360" t="inlineStr"/>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E360" s="5" t="n">
         <v>0.038059</v>
       </c>
@@ -50362,7 +50418,11 @@
           <t>Future income tax recovery (Note 7)</t>
         </is>
       </c>
-      <c r="D423" t="inlineStr"/>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E423" s="5" t="n">
         <v>0.13</v>
       </c>
